--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="D2">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="E2">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="D3">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D3">
         <v>143</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H3">
         <v>426</v>
